--- a/Features_Master_Final_Google_Sheets_v5.xlsx
+++ b/Features_Master_Final_Google_Sheets_v5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41e5c0185c049b29/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41e5c0185c049b29/Desktop/AHH_App_Features/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_EB5549D7A4B16D654BC958B2DE57A8ED9AF67738" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EB058AB-41B4-489C-9E75-D32831D5AEFB}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_EB5549D7A4B16D654BC958B2DE57A8ED9AF67738" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E673790-3C05-4532-B907-6C43049B0D87}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12196,7 +12196,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -12381,43 +12381,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="20">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1855A4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9E2F1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9E2F1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12708,13 +12671,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9E2F1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FFD9E2F1"/>
         </left>
@@ -12727,6 +12683,50 @@
         <bottom style="thin">
           <color rgb="FFD9E2F1"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9E2F1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1855A4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9E2F1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F1"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -12742,25 +12742,29 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{17DE672F-A327-402C-AF58-6F486347EC82}" name="Table1" displayName="Table1" ref="A1:O1339" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="18" tableBorderDxfId="19" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{17DE672F-A327-402C-AF58-6F486347EC82}" name="Table1" displayName="Table1" ref="A1:O1339" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A1:O1339" xr:uid="{17DE672F-A327-402C-AF58-6F486347EC82}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{CB9A3304-FA94-44B2-A0B1-61FFA7C9DF81}" name="Feature_ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{C6FFF590-2FE9-4722-B1AA-3CD448CF9A62}" name="Parent_Feature_ID" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{BF9599AA-37E8-49FF-83FD-4D61D8BFE62D}" name="Level" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{DAE2326C-7743-4CEF-AE31-CD6DB2A7734F}" name="English_Name" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{C8E0A36D-9EE2-400E-A6D5-36CF61DC8FCF}" name="Arabic_Name" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{D9BB0146-F4D3-470A-8AA9-DBF8385E55C6}" name="Category" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{C8E24CE0-DA01-4A76-B34B-B9DB921E3B4B}" name="Main_Feature" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{C8D61744-0DF2-45B4-80A3-7DB163CB46C3}" name="Sub_Section" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{4EBE981D-61D8-4522-A7C3-EC237A573DCC}" name="Phase" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{ADA78B6A-1AD3-4818-92E3-D9295AEB6BE9}" name="Priority" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{A3C271BB-F3FB-4EEF-B3A9-206750E7BECA}" name="Status" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{84A37EFC-27B4-41D0-8BA1-01EB30174437}" name="Calculated_Status" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{F734C126-53ED-4C1D-A6CA-9AA27286ABFE}" name="Completion_Rate" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{2E2D5BE0-ADA3-4683-B84A-BD9DC5018F7C}" name="Is_Countable" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{9884456C-572E-444A-AAF1-9371585FC646}" name="Is_Hidden" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{CB9A3304-FA94-44B2-A0B1-61FFA7C9DF81}" name="Feature_ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{C6FFF590-2FE9-4722-B1AA-3CD448CF9A62}" name="Parent_Feature_ID" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{BF9599AA-37E8-49FF-83FD-4D61D8BFE62D}" name="Level" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{DAE2326C-7743-4CEF-AE31-CD6DB2A7734F}" name="English_Name" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{C8E0A36D-9EE2-400E-A6D5-36CF61DC8FCF}" name="Arabic_Name" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{D9BB0146-F4D3-470A-8AA9-DBF8385E55C6}" name="Category" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{C8E24CE0-DA01-4A76-B34B-B9DB921E3B4B}" name="Main_Feature" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{C8D61744-0DF2-45B4-80A3-7DB163CB46C3}" name="Sub_Section" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{4EBE981D-61D8-4522-A7C3-EC237A573DCC}" name="Phase" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{ADA78B6A-1AD3-4818-92E3-D9295AEB6BE9}" name="Priority" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{A3C271BB-F3FB-4EEF-B3A9-206750E7BECA}" name="Status" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{84A37EFC-27B4-41D0-8BA1-01EB30174437}" name="Calculated_Status" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{F734C126-53ED-4C1D-A6CA-9AA27286ABFE}" name="Completion_Rate" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{2E2D5BE0-ADA3-4683-B84A-BD9DC5018F7C}" name="Is_Countable" dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{9884456C-572E-444A-AAF1-9371585FC646}" name="Is_Hidden" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13258,51 +13262,51 @@
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:18" s="18" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
     </row>
     <row r="6" spans="1:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
@@ -73922,8 +73926,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -75099,6 +75104,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
